--- a/branches/pt/StructureDefinition-PTPackagedMedicinalProduct.xlsx
+++ b/branches/pt/StructureDefinition-PTPackagedMedicinalProduct.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7239" uniqueCount="536">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7239" uniqueCount="538">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-08-24T21:33:25+00:00</t>
+    <t>2022-08-29T19:31:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1500,16 +1500,16 @@
     <t>MedicationKnowledge.definitional.doseForm.coding.userSelected</t>
   </si>
   <si>
-    <t>EDQM</t>
-  </si>
-  <si>
-    <t>http://www.edqm.eu/dose-forms</t>
-  </si>
-  <si>
-    <t>Other</t>
-  </si>
-  <si>
-    <t>http://www.infarmed.pt/dose-forms</t>
+    <t>EDQM-DF</t>
+  </si>
+  <si>
+    <t>http://medigree.net/fhir/mpd5/CodeSystem/dose-form-ontology-cs</t>
+  </si>
+  <si>
+    <t>PT-DF</t>
+  </si>
+  <si>
+    <t>http://medigree.net/fhir/mpd5/CodeSystem/pt-doseform-cs</t>
   </si>
   <si>
     <t>MedicationKnowledge.definitional.doseForm.text</t>
@@ -1531,6 +1531,9 @@
 </t>
   </si>
   <si>
+    <t>EDQM-RoA</t>
+  </si>
+  <si>
     <t>MedicationKnowledge.definitional.intendedRoute.id</t>
   </si>
   <si>
@@ -1567,7 +1570,10 @@
     <t>MedicationKnowledge.definitional.intendedRoute.text</t>
   </si>
   <si>
-    <t>http://www.infarmed.pt/routes</t>
+    <t>PT-RoA</t>
+  </si>
+  <si>
+    <t>http://medigree.net/fhir/mpd5/CodeSystem/pt-route-cs</t>
   </si>
   <si>
     <t>MedicationKnowledge.definitional.ingredient</t>
@@ -20832,7 +20838,7 @@
         <v>484</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>479</v>
+        <v>489</v>
       </c>
       <c r="C171" t="s" s="2">
         <v>74</v>
@@ -20938,7 +20944,7 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B172" s="2"/>
       <c r="C172" t="s" s="2">
@@ -21047,7 +21053,7 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B173" s="2"/>
       <c r="C173" t="s" s="2">
@@ -21158,7 +21164,7 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B174" s="2"/>
       <c r="C174" t="s" s="2">
@@ -21271,7 +21277,7 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B175" s="2"/>
       <c r="C175" t="s" s="2">
@@ -21380,7 +21386,7 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B176" s="2"/>
       <c r="C176" t="s" s="2">
@@ -21491,7 +21497,7 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B177" s="2"/>
       <c r="C177" t="s" s="2">
@@ -21536,7 +21542,7 @@
         <v>74</v>
       </c>
       <c r="R177" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="S177" t="s" s="2">
         <v>74</v>
@@ -21604,7 +21610,7 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B178" s="2"/>
       <c r="C178" t="s" s="2">
@@ -21715,7 +21721,7 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B179" s="2"/>
       <c r="C179" t="s" s="2">
@@ -21826,7 +21832,7 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B180" s="2"/>
       <c r="C180" t="s" s="2">
@@ -21937,7 +21943,7 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B181" s="2"/>
       <c r="C181" t="s" s="2">
@@ -22050,7 +22056,7 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B182" s="2"/>
       <c r="C182" t="s" s="2">
@@ -22166,7 +22172,7 @@
         <v>484</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>481</v>
+        <v>502</v>
       </c>
       <c r="C183" t="s" s="2">
         <v>74</v>
@@ -22272,7 +22278,7 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B184" s="2"/>
       <c r="C184" t="s" s="2">
@@ -22381,7 +22387,7 @@
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B185" s="2"/>
       <c r="C185" t="s" s="2">
@@ -22492,7 +22498,7 @@
     </row>
     <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B186" s="2"/>
       <c r="C186" t="s" s="2">
@@ -22605,7 +22611,7 @@
     </row>
     <row r="187" hidden="true">
       <c r="A187" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B187" s="2"/>
       <c r="C187" t="s" s="2">
@@ -22714,7 +22720,7 @@
     </row>
     <row r="188" hidden="true">
       <c r="A188" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B188" s="2"/>
       <c r="C188" t="s" s="2">
@@ -22825,7 +22831,7 @@
     </row>
     <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B189" s="2"/>
       <c r="C189" t="s" s="2">
@@ -22870,7 +22876,7 @@
         <v>74</v>
       </c>
       <c r="R189" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="S189" t="s" s="2">
         <v>74</v>
@@ -22938,7 +22944,7 @@
     </row>
     <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B190" s="2"/>
       <c r="C190" t="s" s="2">
@@ -23049,7 +23055,7 @@
     </row>
     <row r="191" hidden="true">
       <c r="A191" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B191" s="2"/>
       <c r="C191" t="s" s="2">
@@ -23160,7 +23166,7 @@
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B192" s="2"/>
       <c r="C192" t="s" s="2">
@@ -23271,7 +23277,7 @@
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B193" s="2"/>
       <c r="C193" t="s" s="2">
@@ -23384,7 +23390,7 @@
     </row>
     <row r="194" hidden="true">
       <c r="A194" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B194" s="2"/>
       <c r="C194" t="s" s="2">
@@ -23497,7 +23503,7 @@
     </row>
     <row r="195">
       <c r="A195" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="B195" s="2"/>
       <c r="C195" t="s" s="2">
@@ -23523,10 +23529,10 @@
         <v>259</v>
       </c>
       <c r="K195" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="L195" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="M195" s="2"/>
       <c r="N195" s="2"/>
@@ -23577,7 +23583,7 @@
         <v>74</v>
       </c>
       <c r="AE195" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="AF195" t="s" s="2">
         <v>75</v>
@@ -23606,7 +23612,7 @@
     </row>
     <row r="196" hidden="true">
       <c r="A196" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="B196" s="2"/>
       <c r="C196" t="s" s="2">
@@ -23715,7 +23721,7 @@
     </row>
     <row r="197" hidden="true">
       <c r="A197" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="B197" s="2"/>
       <c r="C197" t="s" s="2">
@@ -23826,7 +23832,7 @@
     </row>
     <row r="198" hidden="true">
       <c r="A198" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="B198" s="2"/>
       <c r="C198" t="s" s="2">
@@ -23939,7 +23945,7 @@
     </row>
     <row r="199">
       <c r="A199" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="B199" s="2"/>
       <c r="C199" t="s" s="2">
@@ -23962,13 +23968,13 @@
         <v>84</v>
       </c>
       <c r="J199" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="K199" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="L199" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="M199" s="2"/>
       <c r="N199" s="2"/>
@@ -24019,7 +24025,7 @@
         <v>74</v>
       </c>
       <c r="AE199" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="AF199" t="s" s="2">
         <v>83</v>
@@ -24048,7 +24054,7 @@
     </row>
     <row r="200">
       <c r="A200" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="B200" s="2"/>
       <c r="C200" t="s" s="2">
@@ -24074,10 +24080,10 @@
         <v>146</v>
       </c>
       <c r="K200" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="L200" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="M200" s="2"/>
       <c r="N200" s="2"/>
@@ -24108,7 +24114,7 @@
       </c>
       <c r="X200" s="2"/>
       <c r="Y200" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="Z200" t="s" s="2">
         <v>74</v>
@@ -24126,7 +24132,7 @@
         <v>74</v>
       </c>
       <c r="AE200" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="AF200" t="s" s="2">
         <v>75</v>
@@ -24155,7 +24161,7 @@
     </row>
     <row r="201">
       <c r="A201" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="B201" s="2"/>
       <c r="C201" t="s" s="2">
@@ -24178,13 +24184,13 @@
         <v>74</v>
       </c>
       <c r="J201" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="K201" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="L201" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="M201" s="2"/>
       <c r="N201" s="2"/>
@@ -24215,7 +24221,7 @@
       </c>
       <c r="X201" s="2"/>
       <c r="Y201" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="Z201" t="s" s="2">
         <v>74</v>
@@ -24233,7 +24239,7 @@
         <v>74</v>
       </c>
       <c r="AE201" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="AF201" t="s" s="2">
         <v>75</v>
@@ -24262,7 +24268,7 @@
     </row>
     <row r="202" hidden="true">
       <c r="A202" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="B202" s="2"/>
       <c r="C202" t="s" s="2">
@@ -24288,10 +24294,10 @@
         <v>259</v>
       </c>
       <c r="K202" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="L202" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="M202" s="2"/>
       <c r="N202" s="2"/>
@@ -24342,7 +24348,7 @@
         <v>74</v>
       </c>
       <c r="AE202" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="AF202" t="s" s="2">
         <v>75</v>
@@ -24371,7 +24377,7 @@
     </row>
     <row r="203" hidden="true">
       <c r="A203" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="B203" s="2"/>
       <c r="C203" t="s" s="2">
@@ -24480,7 +24486,7 @@
     </row>
     <row r="204" hidden="true">
       <c r="A204" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="B204" s="2"/>
       <c r="C204" t="s" s="2">
@@ -24591,7 +24597,7 @@
     </row>
     <row r="205" hidden="true">
       <c r="A205" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="B205" s="2"/>
       <c r="C205" t="s" s="2">
@@ -24704,7 +24710,7 @@
     </row>
     <row r="206" hidden="true">
       <c r="A206" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="B206" s="2"/>
       <c r="C206" t="s" s="2">
@@ -24730,10 +24736,10 @@
         <v>146</v>
       </c>
       <c r="K206" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="L206" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="M206" s="2"/>
       <c r="N206" s="2"/>
@@ -24764,7 +24770,7 @@
       </c>
       <c r="X206" s="2"/>
       <c r="Y206" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="Z206" t="s" s="2">
         <v>74</v>
@@ -24782,7 +24788,7 @@
         <v>74</v>
       </c>
       <c r="AE206" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="AF206" t="s" s="2">
         <v>75</v>
@@ -24811,7 +24817,7 @@
     </row>
     <row r="207" hidden="true">
       <c r="A207" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="B207" s="2"/>
       <c r="C207" t="s" s="2">
@@ -24834,16 +24840,16 @@
         <v>74</v>
       </c>
       <c r="J207" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="K207" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="L207" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="M207" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="N207" s="2"/>
       <c r="O207" t="s" s="2">
@@ -24893,7 +24899,7 @@
         <v>74</v>
       </c>
       <c r="AE207" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="AF207" t="s" s="2">
         <v>75</v>
